--- a/results/final_20260514_v2_summary/emotions_PartialAbstention_summary.xlsx
+++ b/results/final_20260514_v2_summary/emotions_PartialAbstention_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:BU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,100 +476,320 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>afrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>arec__0.0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>arec__0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>arec__0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>arec__0.3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>rec__0.0</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>rec__0.1</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>rec__0.2</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>rec__0.3</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.0</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.1</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.3</t>
         </is>
@@ -623,100 +843,320 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>0.1803±0.0387</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.1754±0.0336</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.1799±0.0321</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.1861±0.0424</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.8305±0.0145</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.8520±0.0111</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.8594±0.0142</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0.8605±0.0162</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.6911±0.0102</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.7031±0.0186</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.6802±0.0257</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.6141±0.0312</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.7448±0.0395</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.7586±0.0315</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.7438±0.0320</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.6956±0.0341</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0.6932±0.0211</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0.7069±0.0213</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>0.6876±0.0238</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.6291±0.0270</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>0.8150±0.0160</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>0.8228±0.0123</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.8014±0.0158</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.7540±0.0152</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.6179±0.0242</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.6379±0.0234</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.6219±0.0254</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.5631±0.0286</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.7044±0.0287</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.7223±0.0207</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.7061±0.0262</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.6613±0.0240</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.6786±0.0132</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.6979±0.0192</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.6657±0.0257</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.5949±0.0294</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.7464±0.0445</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.7691±0.0263</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.7704±0.0407</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.7662±0.0342</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.3826±0.1252</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.4009±0.1269</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.3944±0.1024</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.3913±0.0951</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.7231±0.0236</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.7411±0.0164</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.7296±0.0219</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.6839±0.0206</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.6879±0.0159</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.6992±0.0168</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.6750±0.0241</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.6055±0.0281</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.7632±0.0419</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.7889±0.0239</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.7950±0.0369</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.7871±0.0290</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>0.3878±0.0416</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>0.4364±0.0396</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.4492±0.0448</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>0.4415±0.0623</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>0.3878±0.0416</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.4274±0.0371</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.4156±0.0404</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.3623±0.0487</t>
         </is>
@@ -770,100 +1210,320 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>0.1760±0.0386</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.1717±0.0314</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.1763±0.0299</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.1904±0.0442</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0.8271±0.0155</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.8486±0.0122</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.8564±0.0152</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.8584±0.0179</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.6829±0.0125</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.6941±0.0199</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.6719±0.0268</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.6103±0.0316</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.7510±0.0433</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.7653±0.0322</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.7522±0.0325</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.7080±0.0382</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0.6915±0.0220</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0.7046±0.0224</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>0.6862±0.0255</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.6318±0.0293</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>0.8113±0.0174</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>0.8188±0.0136</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.7973±0.0171</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.7507±0.0167</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.6147±0.0233</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.6334±0.0252</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.6181±0.0267</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.5646±0.0309</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.7022±0.0276</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.7206±0.0220</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.7054±0.0272</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.6625±0.0261</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.6702±0.0105</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.6859±0.0216</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.6563±0.0262</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.5879±0.0309</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.7528±0.0469</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.7774±0.0282</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.7805±0.0382</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.7803±0.0350</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.3707±0.1347</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.3794±0.1086</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.3840±0.0945</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.3995±0.1002</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.7210±0.0237</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.7387±0.0182</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.7278±0.0232</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.6848±0.0240</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.6787±0.0142</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.6889±0.0189</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.6652±0.0250</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.5986±0.0301</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.7701±0.0445</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.7968±0.0254</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.8043±0.0344</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.8017±0.0311</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>0.3777±0.0357</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>0.4236±0.0429</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.4384±0.0460</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>0.4398±0.0643</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>0.3777±0.0357</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.4144±0.0408</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.4041±0.0423</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.3605±0.0498</t>
         </is>
@@ -917,100 +1577,320 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>0.1787±0.0384</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.1751±0.0331</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.1794±0.0302</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.1863±0.0436</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.8308±0.0146</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0.8516±0.0112</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.8592±0.0140</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0.8602±0.0157</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.6911±0.0107</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.7018±0.0188</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.6797±0.0247</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.6135±0.0321</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.7448±0.0395</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.7554±0.0309</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.7429±0.0311</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.6940±0.0368</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0.6935±0.0208</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>0.7049±0.0211</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>0.6869±0.0226</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>0.6281±0.0287</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>0.8152±0.0162</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>0.8223±0.0121</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>0.8012±0.0153</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>0.7532±0.0164</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.6184±0.0231</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.6364±0.0237</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.6214±0.0242</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.5625±0.0294</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.7045±0.0286</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.7212±0.0211</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.7058±0.0257</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.6604±0.0260</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.6789±0.0121</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.6978±0.0198</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.6657±0.0247</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.5944±0.0307</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.7464±0.0445</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.7671±0.0259</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.7698±0.0411</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.7651±0.0355</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>0.3850±0.1242</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.4010±0.1333</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.3940±0.0970</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.3930±0.0937</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.7234±0.0235</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>0.7401±0.0165</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.7292±0.0212</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.6828±0.0222</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.6884±0.0146</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.6989±0.0173</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.6750±0.0233</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>0.6047±0.0294</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.7632±0.0419</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>0.7868±0.0231</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.7942±0.0371</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.7858±0.0301</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
         <is>
           <t>0.3895±0.0393</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>0.4370±0.0407</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>0.4495±0.0440</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>0.4418±0.0616</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>0.3895±0.0393</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>0.4281±0.0382</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>0.4159±0.0399</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>0.3626±0.0485</t>
         </is>
@@ -1064,100 +1944,320 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>0.1769±0.0386</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.1720±0.0311</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.1762±0.0285</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.1921±0.0451</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.8266±0.0150</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.8481±0.0123</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.8563±0.0153</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0.8582±0.0179</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.6821±0.0121</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.6927±0.0200</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.6715±0.0267</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.6099±0.0315</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.7501±0.0423</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.7632±0.0320</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.7519±0.0323</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.7078±0.0396</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0.6908±0.0213</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>0.7030±0.0221</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>0.6858±0.0253</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>0.6314±0.0299</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>0.8107±0.0168</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>0.8181±0.0137</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>0.7972±0.0172</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>0.7503±0.0171</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.6139±0.0226</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.6320±0.0252</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.6178±0.0266</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.5643±0.0307</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>0.7008±0.0266</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>0.7195±0.0224</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>0.7051±0.0275</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0.6619±0.0261</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.6687±0.0109</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.6850±0.0222</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.6560±0.0266</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.5875±0.0308</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.7514±0.0456</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.7763±0.0289</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.7803±0.0386</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.7797±0.0341</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>0.3814±0.1256</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.3803±0.1112</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.3867±0.0915</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.4009±0.1009</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.7200±0.0230</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>0.7377±0.0182</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.7276±0.0236</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.6845±0.0246</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>0.6778±0.0137</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.6880±0.0191</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.6651±0.0253</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>0.5982±0.0307</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>0.7691±0.0436</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>0.7956±0.0253</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.8041±0.0348</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.8015±0.0308</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
         <is>
           <t>0.3777±0.0357</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>0.4229±0.0440</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>0.4381±0.0460</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>0.4398±0.0635</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>0.3777±0.0357</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>0.4137±0.0420</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>0.4037±0.0423</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>0.3605±0.0490</t>
         </is>
@@ -1211,100 +2311,320 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>0.2272±0.0250</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.2267±0.0319</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.2323±0.0379</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.2034±0.0432</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>0.8184±0.0161</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0.8180±0.0141</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.8035±0.0143</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0.7579±0.0220</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.7051±0.0130</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.7069±0.0195</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.6834±0.0221</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.6113±0.0305</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.6998±0.0334</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.6938±0.0364</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.6830±0.0360</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.6530±0.0425</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0.6758±0.0221</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>0.6724±0.0238</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>0.6536±0.0210</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>0.6001±0.0306</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>0.8102±0.0165</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>0.8077±0.0162</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>0.7909±0.0153</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>0.7428±0.0252</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.5972±0.0281</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.5921±0.0278</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.5667±0.0221</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.5009±0.0325</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>0.6823±0.0310</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>0.6765±0.0272</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>0.6535±0.0226</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0.6017±0.0349</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.6939±0.0206</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.6953±0.0241</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.6635±0.0233</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.5840±0.0348</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.6900±0.0399</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.6802±0.0329</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.6657±0.0322</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.6403±0.0439</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>0.4924±0.1145</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.5020±0.1312</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.5010±0.0925</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.4341±0.1032</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>0.7018±0.0270</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>0.6967±0.0234</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.6755±0.0198</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.6189±0.0313</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>0.6991±0.0220</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>0.6973±0.0212</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>0.6675±0.0206</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>0.5887±0.0308</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>0.7054±0.0390</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>0.6967±0.0339</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.6845±0.0317</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.6536±0.0419</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
         <is>
           <t>0.3625±0.0452</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>0.3528±0.0405</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>0.3079±0.0340</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>0.2152±0.0398</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>0.3625±0.0452</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>0.3509±0.0420</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>0.3070±0.0339</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>0.2144±0.0398</t>
         </is>
@@ -1358,100 +2678,320 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>0.1906±0.0294</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.1872±0.0292</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.1671±0.0327</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.1706±0.0390</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.8128±0.0109</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.8083±0.0154</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.7883±0.0169</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.7277±0.0196</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0.6805±0.0050</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.6659±0.0166</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0.6332±0.0237</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0.5478±0.0238</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.7496±0.0318</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.7545±0.0342</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.7694±0.0315</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.7681±0.0343</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0.6867±0.0166</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>0.6793±0.0221</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>0.6655±0.0210</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>0.6105±0.0195</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>0.8043±0.0114</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>0.7977±0.0173</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>0.7751±0.0164</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>0.7104±0.0190</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.6022±0.0208</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.5900±0.0241</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.5685±0.0249</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.4977±0.0228</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>0.6917±0.0242</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0.6874±0.0253</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>0.6725±0.0220</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0.6200±0.0211</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.6623±0.0097</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.6490±0.0217</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.6125±0.0234</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.5294±0.0229</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.7391±0.0357</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.7478±0.0306</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.7610±0.0287</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.7650±0.0341</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0.3938±0.1337</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.3924±0.1009</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.3545±0.0844</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.3667±0.0934</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>0.7095±0.0206</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>0.7049±0.0220</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.6879±0.0191</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.6323±0.0211</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.6698±0.0134</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.6548±0.0192</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0.6173±0.0217</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>0.5332±0.0240</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>0.7549±0.0361</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>0.7639±0.0310</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>0.7775±0.0275</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.7783±0.0327</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
         <is>
           <t>0.3474±0.0375</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>0.3187±0.0356</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>0.2715±0.0439</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>0.1632±0.0370</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>0.3474±0.0375</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>0.3171±0.0361</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>0.2706±0.0430</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>0.1621±0.0359</t>
         </is>
@@ -1505,100 +3045,320 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>0.2357±0.0279</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.2443±0.0355</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.2506±0.0392</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.2192±0.0410</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.8178±0.0140</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.8147±0.0139</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.8001±0.0155</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0.7555±0.0220</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0.7180±0.0174</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.7135±0.0169</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0.6886±0.0247</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0.6154±0.0301</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.6739±0.0308</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.6648±0.0379</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.6569±0.0382</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.6301±0.0387</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0.6693±0.0171</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>0.6604±0.0239</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>0.6421±0.0235</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>0.5903±0.0307</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>0.8095±0.0143</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>0.8040±0.0160</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>0.7870±0.0167</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>0.7399±0.0242</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.5909±0.0197</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.5800±0.0276</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.5550±0.0246</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.4912±0.0347</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>0.6752±0.0286</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>0.6620±0.0308</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>0.6391±0.0256</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>0.5889±0.0327</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.7069±0.0276</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.7009±0.0241</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.6639±0.0254</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.5838±0.0344</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.6621±0.0367</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.6486±0.0367</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.6370±0.0353</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.6144±0.0391</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>0.4876±0.0967</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.5266±0.1241</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.5257±0.0865</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.4653±0.1030</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.6919±0.0231</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>0.6822±0.0253</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.6617±0.0220</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.6067±0.0307</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.7110±0.0234</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.7025±0.0207</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>0.6695±0.0227</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>0.5884±0.0315</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>0.6751±0.0361</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>0.6639±0.0378</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0.6552±0.0339</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.6271±0.0382</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
         <is>
           <t>0.3592±0.0228</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>0.3403±0.0384</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>0.2978±0.0367</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>0.2088±0.0479</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>0.3592±0.0228</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>0.3385±0.0399</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>0.2966±0.0373</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>0.2080±0.0480</t>
         </is>
@@ -1652,100 +3412,320 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>0.1912±0.0310</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.1855±0.0276</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.1654±0.0299</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.1701±0.0399</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>0.8136±0.0118</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.8083±0.0149</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.7894±0.0170</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.7289±0.0191</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0.6813±0.0052</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.6660±0.0162</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0.6344±0.0231</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.5481±0.0235</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.7502±0.0309</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.7542±0.0352</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.7701±0.0326</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.7699±0.0328</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0.6873±0.0151</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>0.6791±0.0218</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>0.6666±0.0218</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>0.6115±0.0188</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>0.8049±0.0126</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>0.7975±0.0168</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>0.7759±0.0166</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>0.7114±0.0180</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.6031±0.0188</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.5900±0.0227</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.5698±0.0259</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.4986±0.0225</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>0.6934±0.0238</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>0.6878±0.0241</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>0.6745±0.0220</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0.6217±0.0206</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.6644±0.0126</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.6499±0.0209</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.6144±0.0219</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.5306±0.0229</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.7399±0.0357</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.7475±0.0307</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.7628±0.0300</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.7676±0.0334</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.3835±0.1303</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.3886±0.0993</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.3490±0.0865</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.3686±0.0983</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>0.7108±0.0201</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>0.7050±0.0212</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.6893±0.0193</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.6338±0.0206</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>0.6713±0.0151</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.6552±0.0181</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.6186±0.0213</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>0.5342±0.0236</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>0.7559±0.0352</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>0.7634±0.0313</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.7789±0.0283</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.7806±0.0322</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
         <is>
           <t>0.3474±0.0346</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>0.3187±0.0305</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>0.2729±0.0468</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>0.1632±0.0371</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>0.3474±0.0346</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>0.3170±0.0317</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>0.2717±0.0457</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>0.1621±0.0361</t>
         </is>
